--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>OMAR ALDAIR</t>
   </si>
 </sst>
 </file>
@@ -773,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +821,52 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920342</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330050470596</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -82,16 +82,34 @@
     <t>VENTURA</t>
   </si>
   <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>PALMA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MARIA DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -791,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -829,10 +847,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -852,10 +870,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -865,6 +883,52 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920240</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -82,34 +82,16 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>PALMA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MARIA DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -673,16 +655,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -790,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -809,7 +794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -847,10 +832,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -870,10 +855,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -883,52 +868,6 @@
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920227</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920240</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
@@ -76,22 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>PALMA</t>
+    <t>CHORA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>VICTOR MANUEL</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -609,16 +609,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>58.33</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,16 +635,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>54.17</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,7 +661,7 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -826,7 +832,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920342</v>
+        <v>19330050470596</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -838,7 +844,7 @@
         <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -849,7 +855,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330050470596</v>
+        <v>19330051920227</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -861,10 +867,10 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,61 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>CHORA</t>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>ABDIEL ANTONIO</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -492,10 +531,10 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -504,7 +543,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -518,10 +557,10 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>21</v>
@@ -530,7 +569,7 @@
         <v>87.5</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -609,19 +648,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>58.33</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -635,19 +674,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>54.17</v>
+        <v>79.17</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -661,7 +700,7 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -673,7 +712,7 @@
         <v>75</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -726,10 +765,10 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -738,7 +777,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -752,10 +791,10 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>21</v>
@@ -764,7 +803,7 @@
         <v>87.5</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -800,7 +839,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,19 +871,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330050470596</v>
+        <v>20330051920341</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -855,25 +894,140 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920227</v>
+        <v>20330051920342</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920235</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920237</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330050470596</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,63 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>ABDIEL ANTONIO</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
   </si>
 </sst>
 </file>
@@ -648,19 +591,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -674,16 +617,16 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -768,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -794,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -820,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -869,167 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920341</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920342</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920227</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920243</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330050470596</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
